--- a/estimation/notsensor/DenseModel/Dense_1st_torch_optimized/IWALQQ_1st_correction/angle/4_fold/39.xlsx
+++ b/estimation/notsensor/DenseModel/Dense_1st_torch_optimized/IWALQQ_1st_correction/angle/4_fold/39.xlsx
@@ -426,13 +426,13 @@
         <v>-5.814388920079002</v>
       </c>
       <c r="E2">
-        <v>-11.01919674973398</v>
+        <v>-10.83946161636955</v>
       </c>
       <c r="F2">
-        <v>-2.394107024815902</v>
+        <v>-1.834978908743903</v>
       </c>
       <c r="G2">
-        <v>-8.139042721847058</v>
+        <v>-7.832967093560495</v>
       </c>
     </row>
     <row r="3" spans="1:7">
@@ -449,13 +449,13 @@
         <v>-6.197401578425348</v>
       </c>
       <c r="E3">
-        <v>-11.93146689552719</v>
+        <v>-12.28497316198796</v>
       </c>
       <c r="F3">
-        <v>-2.192796350220163</v>
+        <v>-1.775386986153909</v>
       </c>
       <c r="G3">
-        <v>-8.237439993971686</v>
+        <v>-7.960750985971511</v>
       </c>
     </row>
     <row r="4" spans="1:7">
@@ -472,13 +472,13 @@
         <v>-6.664096092413382</v>
       </c>
       <c r="E4">
-        <v>-12.17634865596597</v>
+        <v>-11.29878020649354</v>
       </c>
       <c r="F4">
-        <v>-1.959472588975835</v>
+        <v>-1.098711050522452</v>
       </c>
       <c r="G4">
-        <v>-7.803836408555745</v>
+        <v>-7.697813577526968</v>
       </c>
     </row>
     <row r="5" spans="1:7">
@@ -495,13 +495,13 @@
         <v>-7.136067088836518</v>
       </c>
       <c r="E5">
-        <v>-12.55575326527661</v>
+        <v>-12.57697369447656</v>
       </c>
       <c r="F5">
-        <v>-2.123254078387742</v>
+        <v>-1.098737558279341</v>
       </c>
       <c r="G5">
-        <v>-8.165112027136846</v>
+        <v>-7.132042387696593</v>
       </c>
     </row>
     <row r="6" spans="1:7">
@@ -518,13 +518,13 @@
         <v>-7.581828341814474</v>
       </c>
       <c r="E6">
-        <v>-12.90392951783035</v>
+        <v>-12.56399055949656</v>
       </c>
       <c r="F6">
-        <v>-2.07377072321411</v>
+        <v>-1.323164653617603</v>
       </c>
       <c r="G6">
-        <v>-8.013847713246445</v>
+        <v>-7.496704226927041</v>
       </c>
     </row>
     <row r="7" spans="1:7">
@@ -541,13 +541,13 @@
         <v>-7.934203549158539</v>
       </c>
       <c r="E7">
-        <v>-13.23839355108887</v>
+        <v>-12.81343702173508</v>
       </c>
       <c r="F7">
-        <v>-2.051452020280483</v>
+        <v>-0.9379829233572635</v>
       </c>
       <c r="G7">
-        <v>-7.5058096167545</v>
+        <v>-8.091182824180997</v>
       </c>
     </row>
     <row r="8" spans="1:7">
@@ -564,13 +564,13 @@
         <v>-8.140707319249584</v>
       </c>
       <c r="E8">
-        <v>-13.38384813621524</v>
+        <v>-15.12163192276271</v>
       </c>
       <c r="F8">
-        <v>-1.817730642682811</v>
+        <v>-1.014313666055627</v>
       </c>
       <c r="G8">
-        <v>-7.303574807159685</v>
+        <v>-7.292264436444279</v>
       </c>
     </row>
     <row r="9" spans="1:7">
@@ -587,13 +587,13 @@
         <v>-8.150455063214055</v>
       </c>
       <c r="E9">
-        <v>-14.8607918199209</v>
+        <v>-13.61587808742026</v>
       </c>
       <c r="F9">
-        <v>-1.803603664995469</v>
+        <v>-0.8040533100400423</v>
       </c>
       <c r="G9">
-        <v>-7.285075280007535</v>
+        <v>-6.976377955694977</v>
       </c>
     </row>
     <row r="10" spans="1:7">
@@ -610,13 +610,13 @@
         <v>-7.933899140356004</v>
       </c>
       <c r="E10">
-        <v>-15.09007751587727</v>
+        <v>-14.91204961721372</v>
       </c>
       <c r="F10">
-        <v>-1.726312844477261</v>
+        <v>-1.147083565008929</v>
       </c>
       <c r="G10">
-        <v>-7.441327050668293</v>
+        <v>-7.11817594538638</v>
       </c>
     </row>
     <row r="11" spans="1:7">
@@ -633,13 +633,13 @@
         <v>-7.490881022792495</v>
       </c>
       <c r="E11">
-        <v>-15.70419293300546</v>
+        <v>-16.88964780178539</v>
       </c>
       <c r="F11">
-        <v>-1.674911818766148</v>
+        <v>-0.744274176417016</v>
       </c>
       <c r="G11">
-        <v>-6.865653134171515</v>
+        <v>-6.177794252557322</v>
       </c>
     </row>
     <row r="12" spans="1:7">
@@ -656,13 +656,13 @@
         <v>-6.851402832679783</v>
       </c>
       <c r="E12">
-        <v>-16.15771960487364</v>
+        <v>-15.40409548899115</v>
       </c>
       <c r="F12">
-        <v>-1.465953656307765</v>
+        <v>-1.146991616227218</v>
       </c>
       <c r="G12">
-        <v>-6.994047333792587</v>
+        <v>-6.331486670401712</v>
       </c>
     </row>
     <row r="13" spans="1:7">
@@ -679,13 +679,13 @@
         <v>-6.064292650539018</v>
       </c>
       <c r="E13">
-        <v>-17.06409367750886</v>
+        <v>-16.28549049900006</v>
       </c>
       <c r="F13">
-        <v>-0.9942820855211292</v>
+        <v>-1.025490827421601</v>
       </c>
       <c r="G13">
-        <v>-6.180911413038794</v>
+        <v>-5.694545784946983</v>
       </c>
     </row>
     <row r="14" spans="1:7">
@@ -702,13 +702,13 @@
         <v>-5.201291665517519</v>
       </c>
       <c r="E14">
-        <v>-18.82329714611262</v>
+        <v>-17.74218284694342</v>
       </c>
       <c r="F14">
-        <v>-1.343798457253936</v>
+        <v>-0.6245966242649602</v>
       </c>
       <c r="G14">
-        <v>-6.152889780921137</v>
+        <v>-6.075324984477422</v>
       </c>
     </row>
     <row r="15" spans="1:7">
@@ -725,13 +725,13 @@
         <v>-4.335995124216987</v>
       </c>
       <c r="E15">
-        <v>-19.31729026171335</v>
+        <v>-18.37413139471382</v>
       </c>
       <c r="F15">
-        <v>-1.170605057411421</v>
+        <v>0.15249897813827</v>
       </c>
       <c r="G15">
-        <v>-6.197911421938278</v>
+        <v>-5.300487481765469</v>
       </c>
     </row>
     <row r="16" spans="1:7">
@@ -748,13 +748,13 @@
         <v>-3.532884367926923</v>
       </c>
       <c r="E16">
-        <v>-19.84398801659747</v>
+        <v>-19.85229776640154</v>
       </c>
       <c r="F16">
-        <v>-1.002860658344521</v>
+        <v>-0.03062406176160267</v>
       </c>
       <c r="G16">
-        <v>-5.245792799591086</v>
+        <v>-4.816917454442304</v>
       </c>
     </row>
     <row r="17" spans="1:7">
@@ -771,13 +771,13 @@
         <v>-2.845359167300225</v>
       </c>
       <c r="E17">
-        <v>-21.22879083966906</v>
+        <v>-20.45118845391595</v>
       </c>
       <c r="F17">
-        <v>-0.6304473832309331</v>
+        <v>0.6801433343320683</v>
       </c>
       <c r="G17">
-        <v>-5.297760786649571</v>
+        <v>-4.076673870631576</v>
       </c>
     </row>
     <row r="18" spans="1:7">
@@ -794,13 +794,13 @@
         <v>-2.299048510792312</v>
       </c>
       <c r="E18">
-        <v>-20.82928433423837</v>
+        <v>-21.35768479534938</v>
       </c>
       <c r="F18">
-        <v>-0.07282772419943188</v>
+        <v>0.7454567905731981</v>
       </c>
       <c r="G18">
-        <v>-4.49400915955579</v>
+        <v>-4.006249012301215</v>
       </c>
     </row>
     <row r="19" spans="1:7">
@@ -817,13 +817,13 @@
         <v>-1.894944593557468</v>
       </c>
       <c r="E19">
-        <v>-21.51753087087213</v>
+        <v>-21.05679486838373</v>
       </c>
       <c r="F19">
-        <v>-0.0694455000938015</v>
+        <v>0.7600012654315519</v>
       </c>
       <c r="G19">
-        <v>-4.729374463236319</v>
+        <v>-3.239066599487446</v>
       </c>
     </row>
     <row r="20" spans="1:7">
@@ -840,13 +840,13 @@
         <v>-1.619150995327303</v>
       </c>
       <c r="E20">
-        <v>-22.45662316821277</v>
+        <v>-19.73426309139161</v>
       </c>
       <c r="F20">
-        <v>0.335100146574379</v>
+        <v>0.9891044947586167</v>
       </c>
       <c r="G20">
-        <v>-4.257794019491365</v>
+        <v>-2.418213245625839</v>
       </c>
     </row>
     <row r="21" spans="1:7">
@@ -863,13 +863,13 @@
         <v>-1.440388090540956</v>
       </c>
       <c r="E21">
-        <v>-22.34057649329221</v>
+        <v>-22.9783079023704</v>
       </c>
       <c r="F21">
-        <v>0.5439067177980504</v>
+        <v>0.8642430193998416</v>
       </c>
       <c r="G21">
-        <v>-3.495523595352085</v>
+        <v>-3.161954611618935</v>
       </c>
     </row>
     <row r="22" spans="1:7">
@@ -886,13 +886,13 @@
         <v>-1.323739738079225</v>
       </c>
       <c r="E22">
-        <v>-23.27158546452916</v>
+        <v>-23.32701398638304</v>
       </c>
       <c r="F22">
-        <v>0.30133257776666</v>
+        <v>1.394010481247015</v>
       </c>
       <c r="G22">
-        <v>-3.764564075897195</v>
+        <v>-3.909403757974204</v>
       </c>
     </row>
     <row r="23" spans="1:7">
@@ -909,13 +909,13 @@
         <v>-1.236950866813207</v>
       </c>
       <c r="E23">
-        <v>-23.60583665950931</v>
+        <v>-23.977008503074</v>
       </c>
       <c r="F23">
-        <v>0.5509188478627483</v>
+        <v>1.068170506621024</v>
       </c>
       <c r="G23">
-        <v>-4.454900279788768</v>
+        <v>-3.652608796288941</v>
       </c>
     </row>
     <row r="24" spans="1:7">
@@ -932,13 +932,13 @@
         <v>-1.150713801034265</v>
       </c>
       <c r="E24">
-        <v>-24.52256282372607</v>
+        <v>-23.60484945217564</v>
       </c>
       <c r="F24">
-        <v>0.7588614318852998</v>
+        <v>1.870881714221023</v>
       </c>
       <c r="G24">
-        <v>-3.66851287718757</v>
+        <v>-3.172966391172432</v>
       </c>
     </row>
     <row r="25" spans="1:7">
@@ -955,13 +955,13 @@
         <v>-1.05202923957902</v>
       </c>
       <c r="E25">
-        <v>-24.64184282908811</v>
+        <v>-25.03819751660945</v>
       </c>
       <c r="F25">
-        <v>0.9581235538939152</v>
+        <v>1.112175039792539</v>
       </c>
       <c r="G25">
-        <v>-4.170208372405107</v>
+        <v>-1.746744065701073</v>
       </c>
     </row>
     <row r="26" spans="1:7">
@@ -978,13 +978,13 @@
         <v>-0.938290602215604</v>
       </c>
       <c r="E26">
-        <v>-23.69222182967963</v>
+        <v>-24.59942914153227</v>
       </c>
       <c r="F26">
-        <v>0.7779668976634675</v>
+        <v>1.367696562329686</v>
       </c>
       <c r="G26">
-        <v>-3.434758653292728</v>
+        <v>-3.950438714796619</v>
       </c>
     </row>
     <row r="27" spans="1:7">
@@ -1001,13 +1001,13 @@
         <v>-0.8141611067497198</v>
       </c>
       <c r="E27">
-        <v>-25.15865492521348</v>
+        <v>-24.48817359211182</v>
       </c>
       <c r="F27">
-        <v>0.8220459839012348</v>
+        <v>1.473301809042984</v>
       </c>
       <c r="G27">
-        <v>-3.788648242143519</v>
+        <v>-2.97425561353246</v>
       </c>
     </row>
     <row r="28" spans="1:7">
@@ -1024,13 +1024,13 @@
         <v>-0.6962547906018216</v>
       </c>
       <c r="E28">
-        <v>-24.53442289715216</v>
+        <v>-24.75688418277896</v>
       </c>
       <c r="F28">
-        <v>0.4812962243922554</v>
+        <v>1.256589299326994</v>
       </c>
       <c r="G28">
-        <v>-3.822287325570946</v>
+        <v>-3.281151547208883</v>
       </c>
     </row>
     <row r="29" spans="1:7">
@@ -1047,13 +1047,13 @@
         <v>-0.6027695066953789</v>
       </c>
       <c r="E29">
-        <v>-22.87768520991996</v>
+        <v>-22.42265508468123</v>
       </c>
       <c r="F29">
-        <v>0.4821370173060969</v>
+        <v>1.219589440913551</v>
       </c>
       <c r="G29">
-        <v>-3.949500285430618</v>
+        <v>-3.347304255068848</v>
       </c>
     </row>
     <row r="30" spans="1:7">
@@ -1070,13 +1070,13 @@
         <v>-0.551579568337115</v>
       </c>
       <c r="E30">
-        <v>-23.99392235349265</v>
+        <v>-24.17757914534773</v>
       </c>
       <c r="F30">
-        <v>0.6672241163180073</v>
+        <v>1.622275402762447</v>
       </c>
       <c r="G30">
-        <v>-3.40933902987171</v>
+        <v>-2.013048007465606</v>
       </c>
     </row>
     <row r="31" spans="1:7">
@@ -1093,13 +1093,13 @@
         <v>-0.5578724274053609</v>
       </c>
       <c r="E31">
-        <v>-22.74181740426783</v>
+        <v>-23.72810545771641</v>
       </c>
       <c r="F31">
-        <v>0.448488733404381</v>
+        <v>1.143169234535686</v>
       </c>
       <c r="G31">
-        <v>-3.350923442448916</v>
+        <v>-2.480563017698408</v>
       </c>
     </row>
     <row r="32" spans="1:7">
@@ -1116,13 +1116,13 @@
         <v>-0.6264788057173131</v>
       </c>
       <c r="E32">
-        <v>-22.94231559095743</v>
+        <v>-23.27898046258368</v>
       </c>
       <c r="F32">
-        <v>0.5020120364014654</v>
+        <v>0.9137429419215289</v>
       </c>
       <c r="G32">
-        <v>-3.54353442920988</v>
+        <v>-5.497094996385838</v>
       </c>
     </row>
     <row r="33" spans="1:7">
@@ -1139,13 +1139,13 @@
         <v>-0.7548788225137959</v>
       </c>
       <c r="E33">
-        <v>-22.35025837072061</v>
+        <v>-22.08437807630825</v>
       </c>
       <c r="F33">
-        <v>0.08796335888836895</v>
+        <v>0.7813946819762519</v>
       </c>
       <c r="G33">
-        <v>-2.819342581267956</v>
+        <v>-1.817093455935567</v>
       </c>
     </row>
     <row r="34" spans="1:7">
@@ -1162,13 +1162,13 @@
         <v>-0.9330022557730344</v>
       </c>
       <c r="E34">
-        <v>-22.43227356347352</v>
+        <v>-21.64980759663618</v>
       </c>
       <c r="F34">
-        <v>-0.1502601955435185</v>
+        <v>1.556950349377678</v>
       </c>
       <c r="G34">
-        <v>-3.479583421016303</v>
+        <v>-3.793179609117113</v>
       </c>
     </row>
     <row r="35" spans="1:7">
@@ -1185,13 +1185,13 @@
         <v>-1.144307771861895</v>
       </c>
       <c r="E35">
-        <v>-21.33451712232614</v>
+        <v>-22.70577075116677</v>
       </c>
       <c r="F35">
-        <v>0.09950003170715767</v>
+        <v>1.498618373607342</v>
       </c>
       <c r="G35">
-        <v>-3.937162892367106</v>
+        <v>-4.30811483332701</v>
       </c>
     </row>
     <row r="36" spans="1:7">
@@ -1208,13 +1208,13 @@
         <v>-1.373000097725021</v>
       </c>
       <c r="E36">
-        <v>-21.21012899828345</v>
+        <v>-19.60617067561065</v>
       </c>
       <c r="F36">
-        <v>0.5959480715115266</v>
+        <v>1.491701505793966</v>
       </c>
       <c r="G36">
-        <v>-3.729025165186849</v>
+        <v>-2.836106342215159</v>
       </c>
     </row>
     <row r="37" spans="1:7">
@@ -1231,13 +1231,13 @@
         <v>-1.601938335601088</v>
       </c>
       <c r="E37">
-        <v>-20.99264903406508</v>
+        <v>-21.0143902377759</v>
       </c>
       <c r="F37">
-        <v>0.207548962258714</v>
+        <v>1.447761585279869</v>
       </c>
       <c r="G37">
-        <v>-3.860759648355436</v>
+        <v>-4.091685459266036</v>
       </c>
     </row>
     <row r="38" spans="1:7">
@@ -1254,13 +1254,13 @@
         <v>-1.814477180307635</v>
       </c>
       <c r="E38">
-        <v>-21.03642126382322</v>
+        <v>-21.0796229058564</v>
       </c>
       <c r="F38">
-        <v>0.1074548438762413</v>
+        <v>0.9518047673453606</v>
       </c>
       <c r="G38">
-        <v>-3.870708312123672</v>
+        <v>-2.654543228444845</v>
       </c>
     </row>
     <row r="39" spans="1:7">
@@ -1277,13 +1277,13 @@
         <v>-1.999614484669743</v>
       </c>
       <c r="E39">
-        <v>-19.91138982372764</v>
+        <v>-21.12742094900736</v>
       </c>
       <c r="F39">
-        <v>0.3055580798883403</v>
+        <v>1.718046271669709</v>
       </c>
       <c r="G39">
-        <v>-3.680479492214865</v>
+        <v>-3.500392928146301</v>
       </c>
     </row>
     <row r="40" spans="1:7">
@@ -1300,13 +1300,13 @@
         <v>-2.14971486738853</v>
       </c>
       <c r="E40">
-        <v>-19.08129336727761</v>
+        <v>-20.81738350454621</v>
       </c>
       <c r="F40">
-        <v>0.324783658939914</v>
+        <v>1.339394561645638</v>
       </c>
       <c r="G40">
-        <v>-3.709095025434782</v>
+        <v>-3.222348775642075</v>
       </c>
     </row>
     <row r="41" spans="1:7">
@@ -1323,13 +1323,13 @@
         <v>-2.261271015733698</v>
       </c>
       <c r="E41">
-        <v>-18.64382466424063</v>
+        <v>-18.10300259892658</v>
       </c>
       <c r="F41">
-        <v>0.1677434234519893</v>
+        <v>1.361588181101443</v>
       </c>
       <c r="G41">
-        <v>-3.280009682106197</v>
+        <v>-2.913277392071739</v>
       </c>
     </row>
     <row r="42" spans="1:7">
@@ -1346,13 +1346,13 @@
         <v>-2.333440836652424</v>
       </c>
       <c r="E42">
-        <v>-18.45544467399554</v>
+        <v>-18.60835312733854</v>
       </c>
       <c r="F42">
-        <v>0.02749088174919944</v>
+        <v>0.3466409612301818</v>
       </c>
       <c r="G42">
-        <v>-4.291899036380234</v>
+        <v>-3.029311230078382</v>
       </c>
     </row>
     <row r="43" spans="1:7">
@@ -1369,13 +1369,13 @@
         <v>-2.364453902432071</v>
       </c>
       <c r="E43">
-        <v>-18.34616806771645</v>
+        <v>-17.95039755334209</v>
       </c>
       <c r="F43">
-        <v>0.4695880795210872</v>
+        <v>0.9126693777675008</v>
       </c>
       <c r="G43">
-        <v>-4.19637283312012</v>
+        <v>-3.847802104417188</v>
       </c>
     </row>
     <row r="44" spans="1:7">
@@ -1392,13 +1392,13 @@
         <v>-2.354056894262213</v>
       </c>
       <c r="E44">
-        <v>-18.57781309863081</v>
+        <v>-18.08300938618271</v>
       </c>
       <c r="F44">
-        <v>-0.07457392268453325</v>
+        <v>0.5965585782873898</v>
       </c>
       <c r="G44">
-        <v>-4.108797029698541</v>
+        <v>-3.703602260544272</v>
       </c>
     </row>
     <row r="45" spans="1:7">
@@ -1415,13 +1415,13 @@
         <v>-2.305281931566923</v>
       </c>
       <c r="E45">
-        <v>-16.56391013793965</v>
+        <v>-17.48618821128981</v>
       </c>
       <c r="F45">
-        <v>0.3347803967568985</v>
+        <v>0.8375033196374736</v>
       </c>
       <c r="G45">
-        <v>-4.208241011500631</v>
+        <v>-3.034951649939068</v>
       </c>
     </row>
     <row r="46" spans="1:7">
@@ -1438,13 +1438,13 @@
         <v>-2.221808305199644</v>
       </c>
       <c r="E46">
-        <v>-16.75561855658037</v>
+        <v>-15.17243687265477</v>
       </c>
       <c r="F46">
-        <v>0.3887269954968134</v>
+        <v>0.5490798722285334</v>
       </c>
       <c r="G46">
-        <v>-4.855363527454318</v>
+        <v>-2.639774450205784</v>
       </c>
     </row>
     <row r="47" spans="1:7">
@@ -1461,13 +1461,13 @@
         <v>-2.108334274003611</v>
       </c>
       <c r="E47">
-        <v>-16.23123485191417</v>
+        <v>-17.28966149630493</v>
       </c>
       <c r="F47">
-        <v>0.2310364915976912</v>
+        <v>0.7624615166178664</v>
       </c>
       <c r="G47">
-        <v>-4.299203035571558</v>
+        <v>-4.039658410219481</v>
       </c>
     </row>
     <row r="48" spans="1:7">
@@ -1484,13 +1484,13 @@
         <v>-1.971163151722118</v>
       </c>
       <c r="E48">
-        <v>-15.96991925930155</v>
+        <v>-15.49999498305159</v>
       </c>
       <c r="F48">
-        <v>0.03657227358609042</v>
+        <v>1.101586847649956</v>
       </c>
       <c r="G48">
-        <v>-4.40874661733362</v>
+        <v>-3.269801801834764</v>
       </c>
     </row>
     <row r="49" spans="1:7">
@@ -1507,13 +1507,13 @@
         <v>-1.814892673290212</v>
       </c>
       <c r="E49">
-        <v>-15.18141230813797</v>
+        <v>-15.33551627861899</v>
       </c>
       <c r="F49">
-        <v>-0.1056973427425163</v>
+        <v>0.2585424312076487</v>
       </c>
       <c r="G49">
-        <v>-4.22810224559995</v>
+        <v>-3.634959105520688</v>
       </c>
     </row>
     <row r="50" spans="1:7">
@@ -1530,13 +1530,13 @@
         <v>-1.643251643276149</v>
       </c>
       <c r="E50">
-        <v>-14.73937437482724</v>
+        <v>-14.98792419921224</v>
       </c>
       <c r="F50">
-        <v>-0.1110552231038235</v>
+        <v>0.1868952778047139</v>
       </c>
       <c r="G50">
-        <v>-4.726480425820889</v>
+        <v>-4.731513819693077</v>
       </c>
     </row>
     <row r="51" spans="1:7">
@@ -1553,13 +1553,13 @@
         <v>-1.461015751062975</v>
       </c>
       <c r="E51">
-        <v>-13.92358336776745</v>
+        <v>-13.37562895589132</v>
       </c>
       <c r="F51">
-        <v>-0.02416942295898893</v>
+        <v>0.2422882060299169</v>
       </c>
       <c r="G51">
-        <v>-4.618613548275704</v>
+        <v>-3.675081882749578</v>
       </c>
     </row>
     <row r="52" spans="1:7">
@@ -1576,13 +1576,13 @@
         <v>-1.271729994922388</v>
       </c>
       <c r="E52">
-        <v>-13.49525765375195</v>
+        <v>-12.92478766910968</v>
       </c>
       <c r="F52">
-        <v>-0.001202108348969835</v>
+        <v>0.1114359776140957</v>
       </c>
       <c r="G52">
-        <v>-5.167361760655679</v>
+        <v>-3.536043400389668</v>
       </c>
     </row>
     <row r="53" spans="1:7">
@@ -1599,13 +1599,13 @@
         <v>-1.077891649357659</v>
       </c>
       <c r="E53">
-        <v>-12.47581664209321</v>
+        <v>-13.5986653577171</v>
       </c>
       <c r="F53">
-        <v>-0.1999713517529196</v>
+        <v>0.9040527000435803</v>
       </c>
       <c r="G53">
-        <v>-5.263022493999729</v>
+        <v>-3.675994062343104</v>
       </c>
     </row>
     <row r="54" spans="1:7">
@@ -1622,13 +1622,13 @@
         <v>-0.8802904856845594</v>
       </c>
       <c r="E54">
-        <v>-12.63800393867793</v>
+        <v>-12.88402234609264</v>
       </c>
       <c r="F54">
-        <v>-0.2194785757214452</v>
+        <v>-0.09524500285399211</v>
       </c>
       <c r="G54">
-        <v>-4.310464187963571</v>
+        <v>-3.694506714381491</v>
       </c>
     </row>
     <row r="55" spans="1:7">
@@ -1645,13 +1645,13 @@
         <v>-0.6775584578612628</v>
       </c>
       <c r="E55">
-        <v>-12.04513159311972</v>
+        <v>-11.99343906232216</v>
       </c>
       <c r="F55">
-        <v>0.2177014331474247</v>
+        <v>0.5717257802862662</v>
       </c>
       <c r="G55">
-        <v>-5.169678303076646</v>
+        <v>-4.328530593869875</v>
       </c>
     </row>
     <row r="56" spans="1:7">
@@ -1668,13 +1668,13 @@
         <v>-0.4727283109832968</v>
       </c>
       <c r="E56">
-        <v>-11.6519830651958</v>
+        <v>-12.29128585475465</v>
       </c>
       <c r="F56">
-        <v>-0.2579181366809534</v>
+        <v>0.2401245103738045</v>
       </c>
       <c r="G56">
-        <v>-5.565232843289266</v>
+        <v>-5.943764406051486</v>
       </c>
     </row>
     <row r="57" spans="1:7">
@@ -1691,13 +1691,13 @@
         <v>-0.2716731835357935</v>
       </c>
       <c r="E57">
-        <v>-11.12555249027813</v>
+        <v>-12.30080923559279</v>
       </c>
       <c r="F57">
-        <v>-0.4082129764078817</v>
+        <v>0.6211967099488555</v>
       </c>
       <c r="G57">
-        <v>-5.585920945221565</v>
+        <v>-3.378085394517999</v>
       </c>
     </row>
     <row r="58" spans="1:7">
@@ -1714,13 +1714,13 @@
         <v>-0.07990502968620287</v>
       </c>
       <c r="E58">
-        <v>-11.75194007196711</v>
+        <v>-10.58154690773669</v>
       </c>
       <c r="F58">
-        <v>-0.2502217751415432</v>
+        <v>-0.04104906552583446</v>
       </c>
       <c r="G58">
-        <v>-6.490937632082928</v>
+        <v>-5.099305944291236</v>
       </c>
     </row>
     <row r="59" spans="1:7">
@@ -1737,13 +1737,13 @@
         <v>0.09327563655479908</v>
       </c>
       <c r="E59">
-        <v>-10.96550263342504</v>
+        <v>-10.50511532343523</v>
       </c>
       <c r="F59">
-        <v>-0.156108469407283</v>
+        <v>0.2068564471099736</v>
       </c>
       <c r="G59">
-        <v>-5.709130814778714</v>
+        <v>-4.752441450799216</v>
       </c>
     </row>
     <row r="60" spans="1:7">
@@ -1760,13 +1760,13 @@
         <v>0.239946565720613</v>
       </c>
       <c r="E60">
-        <v>-10.49224087183142</v>
+        <v>-10.21518883204215</v>
       </c>
       <c r="F60">
-        <v>-0.654729316909195</v>
+        <v>-0.2472114879997698</v>
       </c>
       <c r="G60">
-        <v>-5.762001137766047</v>
+        <v>-4.21741202575928</v>
       </c>
     </row>
     <row r="61" spans="1:7">
@@ -1783,13 +1783,13 @@
         <v>0.3540556475966296</v>
       </c>
       <c r="E61">
-        <v>-10.15063996353681</v>
+        <v>-10.43884110633297</v>
       </c>
       <c r="F61">
-        <v>-0.3965578470504927</v>
+        <v>-0.3968916791138209</v>
       </c>
       <c r="G61">
-        <v>-5.989452135045195</v>
+        <v>-4.048652238513919</v>
       </c>
     </row>
     <row r="62" spans="1:7">
@@ -1806,13 +1806,13 @@
         <v>0.4288496399439365</v>
       </c>
       <c r="E62">
-        <v>-9.53825895195356</v>
+        <v>-9.821628212983534</v>
       </c>
       <c r="F62">
-        <v>-0.6946433718456864</v>
+        <v>0.5157455395724785</v>
       </c>
       <c r="G62">
-        <v>-5.627516990930646</v>
+        <v>-5.067868560530195</v>
       </c>
     </row>
     <row r="63" spans="1:7">
@@ -1829,13 +1829,13 @@
         <v>0.4606104647021469</v>
       </c>
       <c r="E63">
-        <v>-8.767766270392496</v>
+        <v>-10.38232122224324</v>
       </c>
       <c r="F63">
-        <v>-0.5088852952375085</v>
+        <v>-0.1179546952017406</v>
       </c>
       <c r="G63">
-        <v>-6.051089882039364</v>
+        <v>-4.684808912015941</v>
       </c>
     </row>
     <row r="64" spans="1:7">
@@ -1852,13 +1852,13 @@
         <v>0.4484663469551042</v>
       </c>
       <c r="E64">
-        <v>-9.310159716187204</v>
+        <v>-11.24673445472339</v>
       </c>
       <c r="F64">
-        <v>-1.047556049929971</v>
+        <v>-0.5002942969030748</v>
       </c>
       <c r="G64">
-        <v>-6.442624925841664</v>
+        <v>-4.979475732940315</v>
       </c>
     </row>
     <row r="65" spans="1:7">
@@ -1875,13 +1875,13 @@
         <v>0.3961006829806693</v>
       </c>
       <c r="E65">
-        <v>-8.748991217156695</v>
+        <v>-9.753361467317903</v>
       </c>
       <c r="F65">
-        <v>-0.8369121598068903</v>
+        <v>-0.8008533267630278</v>
       </c>
       <c r="G65">
-        <v>-6.020659833297074</v>
+        <v>-5.647919626587273</v>
       </c>
     </row>
     <row r="66" spans="1:7">
@@ -1898,13 +1898,13 @@
         <v>0.3118276333695093</v>
       </c>
       <c r="E66">
-        <v>-8.814844286176237</v>
+        <v>-8.440991585999003</v>
       </c>
       <c r="F66">
-        <v>-1.174109879892665</v>
+        <v>-0.7084853911464661</v>
       </c>
       <c r="G66">
-        <v>-6.770615832923758</v>
+        <v>-5.567769227554717</v>
       </c>
     </row>
     <row r="67" spans="1:7">
@@ -1921,13 +1921,13 @@
         <v>0.2048157476962568</v>
       </c>
       <c r="E67">
-        <v>-8.467845436864488</v>
+        <v>-8.036847923184462</v>
       </c>
       <c r="F67">
-        <v>-1.11830773817048</v>
+        <v>-0.7025625642164497</v>
       </c>
       <c r="G67">
-        <v>-5.720424779386323</v>
+        <v>-4.702809693491055</v>
       </c>
     </row>
     <row r="68" spans="1:7">
@@ -1944,13 +1944,13 @@
         <v>0.08491818969393275</v>
       </c>
       <c r="E68">
-        <v>-8.865680935386344</v>
+        <v>-9.26769621541728</v>
       </c>
       <c r="F68">
-        <v>-1.134915676229207</v>
+        <v>-0.4774470955664616</v>
       </c>
       <c r="G68">
-        <v>-6.600911053869277</v>
+        <v>-5.690516444871984</v>
       </c>
     </row>
     <row r="69" spans="1:7">
@@ -1967,13 +1967,13 @@
         <v>-0.03885717782363977</v>
       </c>
       <c r="E69">
-        <v>-9.098888289833353</v>
+        <v>-9.244546656290069</v>
       </c>
       <c r="F69">
-        <v>-1.153376672167997</v>
+        <v>-0.8249555047148822</v>
       </c>
       <c r="G69">
-        <v>-6.609721133756387</v>
+        <v>-5.637787214411707</v>
       </c>
     </row>
     <row r="70" spans="1:7">
@@ -1990,13 +1990,13 @@
         <v>-0.1589417357291635</v>
       </c>
       <c r="E70">
-        <v>-9.216918436369273</v>
+        <v>-8.990069059429034</v>
       </c>
       <c r="F70">
-        <v>-1.355224957208152</v>
+        <v>-1.049071133909691</v>
       </c>
       <c r="G70">
-        <v>-5.75690540068423</v>
+        <v>-4.723090923949982</v>
       </c>
     </row>
     <row r="71" spans="1:7">
@@ -2013,13 +2013,13 @@
         <v>-0.2686529142036128</v>
       </c>
       <c r="E71">
-        <v>-8.562472429728768</v>
+        <v>-9.190789141345014</v>
       </c>
       <c r="F71">
-        <v>-1.598753376487568</v>
+        <v>-0.9417503383051957</v>
       </c>
       <c r="G71">
-        <v>-5.988671204314048</v>
+        <v>-6.213277382501157</v>
       </c>
     </row>
     <row r="72" spans="1:7">
@@ -2036,13 +2036,13 @@
         <v>-0.3633912398228978</v>
       </c>
       <c r="E72">
-        <v>-9.554833166821634</v>
+        <v>-9.27362398789332</v>
       </c>
       <c r="F72">
-        <v>-1.269781344711592</v>
+        <v>-1.493906085947831</v>
       </c>
       <c r="G72">
-        <v>-5.580293650247118</v>
+        <v>-5.877286857257137</v>
       </c>
     </row>
     <row r="73" spans="1:7">
@@ -2059,13 +2059,13 @@
         <v>-0.440702657305254</v>
       </c>
       <c r="E73">
-        <v>-9.289808753996734</v>
+        <v>-9.451774155355073</v>
       </c>
       <c r="F73">
-        <v>-1.913127089524008</v>
+        <v>-1.074179778255947</v>
       </c>
       <c r="G73">
-        <v>-5.538812447292617</v>
+        <v>-5.4722594304024</v>
       </c>
     </row>
     <row r="74" spans="1:7">
@@ -2082,13 +2082,13 @@
         <v>-0.5002850663033093</v>
       </c>
       <c r="E74">
-        <v>-10.20660737379761</v>
+        <v>-10.48838714045089</v>
       </c>
       <c r="F74">
-        <v>-2.092981391652434</v>
+        <v>-1.225230917421631</v>
       </c>
       <c r="G74">
-        <v>-5.237832556087873</v>
+        <v>-4.626285044281685</v>
       </c>
     </row>
     <row r="75" spans="1:7">
@@ -2105,13 +2105,13 @@
         <v>-0.5445427785350276</v>
       </c>
       <c r="E75">
-        <v>-10.2701237502292</v>
+        <v>-10.25638436008993</v>
       </c>
       <c r="F75">
-        <v>-2.032991852709096</v>
+        <v>-1.119552774376887</v>
       </c>
       <c r="G75">
-        <v>-5.13360783447367</v>
+        <v>-4.484388617943498</v>
       </c>
     </row>
     <row r="76" spans="1:7">
@@ -2128,13 +2128,13 @@
         <v>-0.5782912360841735</v>
       </c>
       <c r="E76">
-        <v>-10.63541763453193</v>
+        <v>-10.58368887594232</v>
       </c>
       <c r="F76">
-        <v>-1.78350084486433</v>
+        <v>-1.192907192996992</v>
       </c>
       <c r="G76">
-        <v>-4.773077053186563</v>
+        <v>-4.436942154193928</v>
       </c>
     </row>
     <row r="77" spans="1:7">
@@ -2151,13 +2151,13 @@
         <v>-0.6081124556854328</v>
       </c>
       <c r="E77">
-        <v>-9.981569386460443</v>
+        <v>-11.44318871412414</v>
       </c>
       <c r="F77">
-        <v>-2.226902721295627</v>
+        <v>-1.871390626301358</v>
       </c>
       <c r="G77">
-        <v>-5.299217649021964</v>
+        <v>-4.291108261984408</v>
       </c>
     </row>
     <row r="78" spans="1:7">
@@ -2174,13 +2174,13 @@
         <v>-0.6437157086844472</v>
       </c>
       <c r="E78">
-        <v>-10.92034469062055</v>
+        <v>-11.12362788882487</v>
       </c>
       <c r="F78">
-        <v>-1.8925007411943</v>
+        <v>-1.591502676610864</v>
       </c>
       <c r="G78">
-        <v>-4.549028682664559</v>
+        <v>-4.69775661228951</v>
       </c>
     </row>
     <row r="79" spans="1:7">
@@ -2197,13 +2197,13 @@
         <v>-0.6942123697836335</v>
       </c>
       <c r="E79">
-        <v>-11.50477596062846</v>
+        <v>-13.20504586849639</v>
       </c>
       <c r="F79">
-        <v>-2.014609551673573</v>
+        <v>-1.392781478516276</v>
       </c>
       <c r="G79">
-        <v>-4.383431993002503</v>
+        <v>-5.624593422521181</v>
       </c>
     </row>
     <row r="80" spans="1:7">
@@ -2220,13 +2220,13 @@
         <v>-0.7661677273467197</v>
       </c>
       <c r="E80">
-        <v>-11.16509965378711</v>
+        <v>-11.05976281989469</v>
       </c>
       <c r="F80">
-        <v>-2.303799238930103</v>
+        <v>-1.629827922868786</v>
       </c>
       <c r="G80">
-        <v>-4.601669320142731</v>
+        <v>-3.73487230200578</v>
       </c>
     </row>
     <row r="81" spans="1:7">
@@ -2243,13 +2243,13 @@
         <v>-0.8673928597226399</v>
       </c>
       <c r="E81">
-        <v>-11.9223193780317</v>
+        <v>-11.79896374606276</v>
       </c>
       <c r="F81">
-        <v>-2.028392756888754</v>
+        <v>-2.217260524727041</v>
       </c>
       <c r="G81">
-        <v>-3.659256551168376</v>
+        <v>-3.679455751088318</v>
       </c>
     </row>
     <row r="82" spans="1:7">
@@ -2266,13 +2266,13 @@
         <v>-1.00175316230315</v>
       </c>
       <c r="E82">
-        <v>-14.19604353491295</v>
+        <v>-13.76259158832076</v>
       </c>
       <c r="F82">
-        <v>-2.215197061526667</v>
+        <v>-2.205575574143151</v>
       </c>
       <c r="G82">
-        <v>-4.048478333771268</v>
+        <v>-4.04521679954118</v>
       </c>
     </row>
     <row r="83" spans="1:7">
@@ -2289,13 +2289,13 @@
         <v>-1.171637187694071</v>
       </c>
       <c r="E83">
-        <v>-13.53609090387911</v>
+        <v>-13.81173005977799</v>
       </c>
       <c r="F83">
-        <v>-2.445101322132239</v>
+        <v>-2.200029654381408</v>
       </c>
       <c r="G83">
-        <v>-3.29564798405851</v>
+        <v>-4.552073656271724</v>
       </c>
     </row>
     <row r="84" spans="1:7">
@@ -2312,13 +2312,13 @@
         <v>-1.37998315127634</v>
       </c>
       <c r="E84">
-        <v>-15.46033460769241</v>
+        <v>-16.48782724613678</v>
       </c>
       <c r="F84">
-        <v>-2.761403474482397</v>
+        <v>-1.394930263559138</v>
       </c>
       <c r="G84">
-        <v>-4.466955487798169</v>
+        <v>-3.33659762912038</v>
       </c>
     </row>
     <row r="85" spans="1:7">
@@ -2335,13 +2335,13 @@
         <v>-1.624307165495843</v>
       </c>
       <c r="E85">
-        <v>-15.54721791000357</v>
+        <v>-16.80380604849599</v>
       </c>
       <c r="F85">
-        <v>-2.472492947040611</v>
+        <v>-1.868408503651279</v>
       </c>
       <c r="G85">
-        <v>-3.291936922474778</v>
+        <v>-3.898444477965658</v>
       </c>
     </row>
     <row r="86" spans="1:7">
@@ -2358,13 +2358,13 @@
         <v>-1.902253519104432</v>
       </c>
       <c r="E86">
-        <v>-16.83115803150232</v>
+        <v>-16.70977228572671</v>
       </c>
       <c r="F86">
-        <v>-2.942033956867246</v>
+        <v>-2.552990377775055</v>
       </c>
       <c r="G86">
-        <v>-3.32058526791029</v>
+        <v>-3.305757427683159</v>
       </c>
     </row>
     <row r="87" spans="1:7">
@@ -2381,13 +2381,13 @@
         <v>-2.212670400734906</v>
       </c>
       <c r="E87">
-        <v>-17.75016654661894</v>
+        <v>-19.09773625639946</v>
       </c>
       <c r="F87">
-        <v>-2.83431968674642</v>
+        <v>-2.018767127668224</v>
       </c>
       <c r="G87">
-        <v>-3.178275407655613</v>
+        <v>-4.607634580937801</v>
       </c>
     </row>
     <row r="88" spans="1:7">
@@ -2404,13 +2404,13 @@
         <v>-2.550783729518631</v>
       </c>
       <c r="E88">
-        <v>-19.84153811215932</v>
+        <v>-19.68658731703886</v>
       </c>
       <c r="F88">
-        <v>-2.951525390568523</v>
+        <v>-2.283226734481577</v>
       </c>
       <c r="G88">
-        <v>-3.212882451443077</v>
+        <v>-3.497344673317577</v>
       </c>
     </row>
     <row r="89" spans="1:7">
@@ -2427,13 +2427,13 @@
         <v>-2.914061888886188</v>
       </c>
       <c r="E89">
-        <v>-20.77414563472098</v>
+        <v>-23.23250926231697</v>
       </c>
       <c r="F89">
-        <v>-3.067890301476783</v>
+        <v>-2.525411541833651</v>
       </c>
       <c r="G89">
-        <v>-3.248299956955723</v>
+        <v>-3.760603641474945</v>
       </c>
     </row>
     <row r="90" spans="1:7">
@@ -2450,13 +2450,13 @@
         <v>-3.296418214711234</v>
       </c>
       <c r="E90">
-        <v>-22.2399719147378</v>
+        <v>-25.23946554388036</v>
       </c>
       <c r="F90">
-        <v>-3.20330103571021</v>
+        <v>-1.789145340347006</v>
       </c>
       <c r="G90">
-        <v>-3.426339038771193</v>
+        <v>-3.729832345690473</v>
       </c>
     </row>
     <row r="91" spans="1:7">
@@ -2473,13 +2473,13 @@
         <v>-3.68577016171175</v>
       </c>
       <c r="E91">
-        <v>-23.95511333124692</v>
+        <v>-23.84696431499573</v>
       </c>
       <c r="F91">
-        <v>-3.128489518828581</v>
+        <v>-2.782695830203955</v>
       </c>
       <c r="G91">
-        <v>-2.871412286194784</v>
+        <v>-1.928385928788813</v>
       </c>
     </row>
     <row r="92" spans="1:7">
@@ -2496,13 +2496,13 @@
         <v>-4.073324888627178</v>
       </c>
       <c r="E92">
-        <v>-26.06233455581414</v>
+        <v>-27.39246058371712</v>
       </c>
       <c r="F92">
-        <v>-3.618981597006822</v>
+        <v>-2.733691271389142</v>
       </c>
       <c r="G92">
-        <v>-3.352226087408015</v>
+        <v>-3.792441334266238</v>
       </c>
     </row>
     <row r="93" spans="1:7">
@@ -2519,13 +2519,13 @@
         <v>-4.446502267359447</v>
       </c>
       <c r="E93">
-        <v>-27.58348520278268</v>
+        <v>-28.19984674301867</v>
       </c>
       <c r="F93">
-        <v>-3.521521686965251</v>
+        <v>-3.077559834169662</v>
       </c>
       <c r="G93">
-        <v>-3.137020608988715</v>
+        <v>-4.203414334586688</v>
       </c>
     </row>
     <row r="94" spans="1:7">
@@ -2542,13 +2542,13 @@
         <v>-4.788599055952869</v>
       </c>
       <c r="E94">
-        <v>-29.58450012644801</v>
+        <v>-30.8591998967341</v>
       </c>
       <c r="F94">
-        <v>-3.723388196088268</v>
+        <v>-3.106984272684503</v>
       </c>
       <c r="G94">
-        <v>-3.626703552077125</v>
+        <v>-3.49809279183313</v>
       </c>
     </row>
     <row r="95" spans="1:7">
@@ -2565,13 +2565,13 @@
         <v>-5.091187107213663</v>
       </c>
       <c r="E95">
-        <v>-32.02057686921525</v>
+        <v>-33.54534803115292</v>
       </c>
       <c r="F95">
-        <v>-3.268728806652926</v>
+        <v>-2.818509466496589</v>
       </c>
       <c r="G95">
-        <v>-3.410973078208313</v>
+        <v>-4.487486091095614</v>
       </c>
     </row>
     <row r="96" spans="1:7">
@@ -2588,13 +2588,13 @@
         <v>-5.342260687287572</v>
       </c>
       <c r="E96">
-        <v>-33.68469596907995</v>
+        <v>-34.37517277916248</v>
       </c>
       <c r="F96">
-        <v>-3.540122676995114</v>
+        <v>-3.053840361957901</v>
       </c>
       <c r="G96">
-        <v>-3.026453286100106</v>
+        <v>-4.411709560401798</v>
       </c>
     </row>
     <row r="97" spans="1:7">
@@ -2611,13 +2611,13 @@
         <v>-5.536879276407932</v>
       </c>
       <c r="E97">
-        <v>-36.50183474264463</v>
+        <v>-37.77579863590448</v>
       </c>
       <c r="F97">
-        <v>-3.651084147334914</v>
+        <v>-3.637426853964958</v>
       </c>
       <c r="G97">
-        <v>-3.728418139198352</v>
+        <v>-3.771474328501386</v>
       </c>
     </row>
     <row r="98" spans="1:7">
@@ -2634,13 +2634,13 @@
         <v>-5.667942985900042</v>
       </c>
       <c r="E98">
-        <v>-38.86578421565471</v>
+        <v>-38.38918723295444</v>
       </c>
       <c r="F98">
-        <v>-3.93861295794883</v>
+        <v>-3.809599705167224</v>
       </c>
       <c r="G98">
-        <v>-4.03151113708738</v>
+        <v>-2.644778313083938</v>
       </c>
     </row>
     <row r="99" spans="1:7">
@@ -2657,13 +2657,13 @@
         <v>-5.738221512064812</v>
       </c>
       <c r="E99">
-        <v>-41.03744562535108</v>
+        <v>-43.65767502787724</v>
       </c>
       <c r="F99">
-        <v>-4.037647594423122</v>
+        <v>-3.705929524706866</v>
       </c>
       <c r="G99">
-        <v>-4.038765917955311</v>
+        <v>-3.577524603344168</v>
       </c>
     </row>
     <row r="100" spans="1:7">
@@ -2680,13 +2680,13 @@
         <v>-5.728074218809635</v>
       </c>
       <c r="E100">
-        <v>-44.13150284872182</v>
+        <v>-45.01119968097785</v>
       </c>
       <c r="F100">
-        <v>-4.168637331827808</v>
+        <v>-3.28337102886481</v>
       </c>
       <c r="G100">
-        <v>-3.963415946064223</v>
+        <v>-4.290081239636301</v>
       </c>
     </row>
     <row r="101" spans="1:7">
@@ -2703,13 +2703,13 @@
         <v>-5.658226695938156</v>
       </c>
       <c r="E101">
-        <v>-46.1144219902525</v>
+        <v>-46.27097586517166</v>
       </c>
       <c r="F101">
-        <v>-4.350769644313933</v>
+        <v>-4.040533626454476</v>
       </c>
       <c r="G101">
-        <v>-4.140195038800867</v>
+        <v>-4.456987136700576</v>
       </c>
     </row>
     <row r="102" spans="1:7">
@@ -2726,13 +2726,13 @@
         <v>-5.487990818743707</v>
       </c>
       <c r="E102">
-        <v>-49.57943255831705</v>
+        <v>-48.76954328500776</v>
       </c>
       <c r="F102">
-        <v>-4.37207939575095</v>
+        <v>-4.024236326171798</v>
       </c>
       <c r="G102">
-        <v>-4.669977790567251</v>
+        <v>-3.590482147282415</v>
       </c>
     </row>
   </sheetData>
